--- a/MPA.xlsx
+++ b/MPA.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9793" uniqueCount="2314">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9772" uniqueCount="2314">
   <si>
     <t>Site ID</t>
   </si>
@@ -31549,8 +31549,8 @@
       <c r="E262" t="s">
         <v>1819</v>
       </c>
-      <c r="F262" t="s">
-        <v>1801</v>
+      <c r="F262">
+        <v>2017</v>
       </c>
       <c r="G262" t="s">
         <v>538</v>
@@ -31632,8 +31632,8 @@
       <c r="E263" t="s">
         <v>1832</v>
       </c>
-      <c r="F263" t="s">
-        <v>1801</v>
+      <c r="F263">
+        <v>2012</v>
       </c>
       <c r="G263" t="s">
         <v>538</v>
@@ -31724,8 +31724,8 @@
       <c r="E264" t="s">
         <v>1844</v>
       </c>
-      <c r="F264" t="s">
-        <v>1801</v>
+      <c r="F264">
+        <v>2012</v>
       </c>
       <c r="G264" t="s">
         <v>538</v>
@@ -31807,8 +31807,8 @@
       <c r="E265" t="s">
         <v>1851</v>
       </c>
-      <c r="F265" t="s">
-        <v>1801</v>
+      <c r="F265">
+        <v>2012</v>
       </c>
       <c r="G265" t="s">
         <v>538</v>
@@ -31899,8 +31899,8 @@
       <c r="E266" t="s">
         <v>1858</v>
       </c>
-      <c r="F266" t="s">
-        <v>1801</v>
+      <c r="F266">
+        <v>2012</v>
       </c>
       <c r="G266" t="s">
         <v>538</v>
@@ -31991,8 +31991,8 @@
       <c r="E267" t="s">
         <v>1868</v>
       </c>
-      <c r="F267" t="s">
-        <v>1801</v>
+      <c r="F267">
+        <v>2014</v>
       </c>
       <c r="G267" t="s">
         <v>538</v>
@@ -32083,8 +32083,8 @@
       <c r="E268" t="s">
         <v>1875</v>
       </c>
-      <c r="F268" t="s">
-        <v>1801</v>
+      <c r="F268">
+        <v>2012</v>
       </c>
       <c r="G268" t="s">
         <v>538</v>
@@ -32175,8 +32175,8 @@
       <c r="E269" t="s">
         <v>1883</v>
       </c>
-      <c r="F269" t="s">
-        <v>1801</v>
+      <c r="F269">
+        <v>2014</v>
       </c>
       <c r="G269" t="s">
         <v>538</v>
@@ -32267,8 +32267,8 @@
       <c r="E270" t="s">
         <v>1887</v>
       </c>
-      <c r="F270" t="s">
-        <v>1801</v>
+      <c r="F270">
+        <v>2012</v>
       </c>
       <c r="G270" t="s">
         <v>538</v>
@@ -32356,8 +32356,8 @@
       <c r="E271" t="s">
         <v>1896</v>
       </c>
-      <c r="F271" t="s">
-        <v>1801</v>
+      <c r="F271">
+        <v>2014</v>
       </c>
       <c r="G271" t="s">
         <v>538</v>
@@ -32439,8 +32439,8 @@
       <c r="E272" t="s">
         <v>1902</v>
       </c>
-      <c r="F272" t="s">
-        <v>1801</v>
+      <c r="F272">
+        <v>2021</v>
       </c>
       <c r="G272" t="s">
         <v>538</v>
@@ -32522,8 +32522,8 @@
       <c r="E273" t="s">
         <v>1907</v>
       </c>
-      <c r="F273" t="s">
-        <v>1801</v>
+      <c r="F273">
+        <v>2004</v>
       </c>
       <c r="G273" t="s">
         <v>538</v>
@@ -32688,8 +32688,8 @@
       <c r="E275" t="s">
         <v>1918</v>
       </c>
-      <c r="F275" t="s">
-        <v>1801</v>
+      <c r="F275">
+        <v>2008</v>
       </c>
       <c r="G275" t="s">
         <v>538</v>
@@ -32780,8 +32780,8 @@
       <c r="E276" t="s">
         <v>1924</v>
       </c>
-      <c r="F276" t="s">
-        <v>1801</v>
+      <c r="F276">
+        <v>2004</v>
       </c>
       <c r="G276" t="s">
         <v>538</v>
@@ -32863,8 +32863,8 @@
       <c r="E277" t="s">
         <v>1928</v>
       </c>
-      <c r="F277" t="s">
-        <v>1801</v>
+      <c r="F277">
+        <v>2008</v>
       </c>
       <c r="G277" t="s">
         <v>538</v>
@@ -32955,8 +32955,8 @@
       <c r="E278" t="s">
         <v>1935</v>
       </c>
-      <c r="F278" t="s">
-        <v>1801</v>
+      <c r="F278">
+        <v>2012</v>
       </c>
       <c r="G278" t="s">
         <v>538</v>
@@ -33047,8 +33047,8 @@
       <c r="E279" t="s">
         <v>1942</v>
       </c>
-      <c r="F279" t="s">
-        <v>1801</v>
+      <c r="F279">
+        <v>2004</v>
       </c>
       <c r="G279" t="s">
         <v>538</v>
@@ -33130,8 +33130,8 @@
       <c r="E280" t="s">
         <v>1945</v>
       </c>
-      <c r="F280" t="s">
-        <v>1801</v>
+      <c r="F280">
+        <v>2009</v>
       </c>
       <c r="G280" t="s">
         <v>538</v>
@@ -33222,8 +33222,8 @@
       <c r="E281" t="s">
         <v>1953</v>
       </c>
-      <c r="F281" t="s">
-        <v>1801</v>
+      <c r="F281">
+        <v>2012</v>
       </c>
       <c r="G281" t="s">
         <v>538</v>
@@ -33305,8 +33305,8 @@
       <c r="E282" t="s">
         <v>1958</v>
       </c>
-      <c r="F282" t="s">
-        <v>1801</v>
+      <c r="F282">
+        <v>2012</v>
       </c>
       <c r="G282" t="s">
         <v>538</v>
@@ -33397,8 +33397,8 @@
       <c r="E283" t="s">
         <v>1965</v>
       </c>
-      <c r="F283" t="s">
-        <v>1801</v>
+      <c r="F283">
+        <v>2012</v>
       </c>
       <c r="G283" t="s">
         <v>538</v>

--- a/MPA.xlsx
+++ b/MPA.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9772" uniqueCount="2314">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9793" uniqueCount="2314">
   <si>
     <t>Site ID</t>
   </si>
@@ -31549,8 +31549,8 @@
       <c r="E262" t="s">
         <v>1819</v>
       </c>
-      <c r="F262">
-        <v>2017</v>
+      <c r="F262" t="s">
+        <v>1801</v>
       </c>
       <c r="G262" t="s">
         <v>538</v>
@@ -31632,8 +31632,8 @@
       <c r="E263" t="s">
         <v>1832</v>
       </c>
-      <c r="F263">
-        <v>2012</v>
+      <c r="F263" t="s">
+        <v>1801</v>
       </c>
       <c r="G263" t="s">
         <v>538</v>
@@ -31724,8 +31724,8 @@
       <c r="E264" t="s">
         <v>1844</v>
       </c>
-      <c r="F264">
-        <v>2012</v>
+      <c r="F264" t="s">
+        <v>1801</v>
       </c>
       <c r="G264" t="s">
         <v>538</v>
@@ -31807,8 +31807,8 @@
       <c r="E265" t="s">
         <v>1851</v>
       </c>
-      <c r="F265">
-        <v>2012</v>
+      <c r="F265" t="s">
+        <v>1801</v>
       </c>
       <c r="G265" t="s">
         <v>538</v>
@@ -31899,8 +31899,8 @@
       <c r="E266" t="s">
         <v>1858</v>
       </c>
-      <c r="F266">
-        <v>2012</v>
+      <c r="F266" t="s">
+        <v>1801</v>
       </c>
       <c r="G266" t="s">
         <v>538</v>
@@ -31991,8 +31991,8 @@
       <c r="E267" t="s">
         <v>1868</v>
       </c>
-      <c r="F267">
-        <v>2014</v>
+      <c r="F267" t="s">
+        <v>1801</v>
       </c>
       <c r="G267" t="s">
         <v>538</v>
@@ -32083,8 +32083,8 @@
       <c r="E268" t="s">
         <v>1875</v>
       </c>
-      <c r="F268">
-        <v>2012</v>
+      <c r="F268" t="s">
+        <v>1801</v>
       </c>
       <c r="G268" t="s">
         <v>538</v>
@@ -32175,8 +32175,8 @@
       <c r="E269" t="s">
         <v>1883</v>
       </c>
-      <c r="F269">
-        <v>2014</v>
+      <c r="F269" t="s">
+        <v>1801</v>
       </c>
       <c r="G269" t="s">
         <v>538</v>
@@ -32267,8 +32267,8 @@
       <c r="E270" t="s">
         <v>1887</v>
       </c>
-      <c r="F270">
-        <v>2012</v>
+      <c r="F270" t="s">
+        <v>1801</v>
       </c>
       <c r="G270" t="s">
         <v>538</v>
@@ -32356,8 +32356,8 @@
       <c r="E271" t="s">
         <v>1896</v>
       </c>
-      <c r="F271">
-        <v>2014</v>
+      <c r="F271" t="s">
+        <v>1801</v>
       </c>
       <c r="G271" t="s">
         <v>538</v>
@@ -32439,8 +32439,8 @@
       <c r="E272" t="s">
         <v>1902</v>
       </c>
-      <c r="F272">
-        <v>2021</v>
+      <c r="F272" t="s">
+        <v>1801</v>
       </c>
       <c r="G272" t="s">
         <v>538</v>
@@ -32522,8 +32522,8 @@
       <c r="E273" t="s">
         <v>1907</v>
       </c>
-      <c r="F273">
-        <v>2004</v>
+      <c r="F273" t="s">
+        <v>1801</v>
       </c>
       <c r="G273" t="s">
         <v>538</v>
@@ -32688,8 +32688,8 @@
       <c r="E275" t="s">
         <v>1918</v>
       </c>
-      <c r="F275">
-        <v>2008</v>
+      <c r="F275" t="s">
+        <v>1801</v>
       </c>
       <c r="G275" t="s">
         <v>538</v>
@@ -32780,8 +32780,8 @@
       <c r="E276" t="s">
         <v>1924</v>
       </c>
-      <c r="F276">
-        <v>2004</v>
+      <c r="F276" t="s">
+        <v>1801</v>
       </c>
       <c r="G276" t="s">
         <v>538</v>
@@ -32863,8 +32863,8 @@
       <c r="E277" t="s">
         <v>1928</v>
       </c>
-      <c r="F277">
-        <v>2008</v>
+      <c r="F277" t="s">
+        <v>1801</v>
       </c>
       <c r="G277" t="s">
         <v>538</v>
@@ -32955,8 +32955,8 @@
       <c r="E278" t="s">
         <v>1935</v>
       </c>
-      <c r="F278">
-        <v>2012</v>
+      <c r="F278" t="s">
+        <v>1801</v>
       </c>
       <c r="G278" t="s">
         <v>538</v>
@@ -33047,8 +33047,8 @@
       <c r="E279" t="s">
         <v>1942</v>
       </c>
-      <c r="F279">
-        <v>2004</v>
+      <c r="F279" t="s">
+        <v>1801</v>
       </c>
       <c r="G279" t="s">
         <v>538</v>
@@ -33130,8 +33130,8 @@
       <c r="E280" t="s">
         <v>1945</v>
       </c>
-      <c r="F280">
-        <v>2009</v>
+      <c r="F280" t="s">
+        <v>1801</v>
       </c>
       <c r="G280" t="s">
         <v>538</v>
@@ -33222,8 +33222,8 @@
       <c r="E281" t="s">
         <v>1953</v>
       </c>
-      <c r="F281">
-        <v>2012</v>
+      <c r="F281" t="s">
+        <v>1801</v>
       </c>
       <c r="G281" t="s">
         <v>538</v>
@@ -33305,8 +33305,8 @@
       <c r="E282" t="s">
         <v>1958</v>
       </c>
-      <c r="F282">
-        <v>2012</v>
+      <c r="F282" t="s">
+        <v>1801</v>
       </c>
       <c r="G282" t="s">
         <v>538</v>
@@ -33397,8 +33397,8 @@
       <c r="E283" t="s">
         <v>1965</v>
       </c>
-      <c r="F283">
-        <v>2012</v>
+      <c r="F283" t="s">
+        <v>1801</v>
       </c>
       <c r="G283" t="s">
         <v>538</v>
